--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>07/05/2028</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Janidir ia</t>
+          <t>Jdwdba</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>LCK</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G67J</t>
+          <t>G67D</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2028</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G67D</t>
+          <t>G67A</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jdwdba</t>
+          <t>Sandra</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LCK</t>
+          <t>DOE</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4401</v>
+        <v>116</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -730,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>SANDRA</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>116</v>
+        <v>0.16</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58220.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
